--- a/ai_logs/LuongTrieuVy_ai_log.xlsx
+++ b/ai_logs/LuongTrieuVy_ai_log.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="179">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -348,6 +348,71 @@
   </si>
   <si>
     <t>Tôi dùng câu trả lời của AI như tài liệu tham khảo ban đầu để hiểu tổng quan các class trong dự án. Tôi không dùng ngay làm bản class diagram cuối cùng mà tiếp tục hỏi thêm về số lượng class, cách chia MVC và vai trò từng nhóm class để kiểm tra lại. Nhờ đó tôi hiểu rõ hơn kiến trúc tổng thể trước khi thiết kế bản cuối.</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>KNOWLEDGE BUILDING / BUSINESS LOGIC</t>
+  </si>
+  <si>
+    <t>Payroll Processing / SalaryCalculator</t>
+  </si>
+  <si>
+    <t>Tôi cần hiểu công thức tính lương cơ bản để thiết kế phần Payroll Processing và xác định logic nào sẽ nằm trong class SalaryCalculator</t>
+  </si>
+  <si>
+    <t>công thức tính lương</t>
+  </si>
+  <si>
+    <t>AI đề xuất công thức tính lương gồm: Gross Salary = Base Salary + Overtime Pay + Bonus - Absent Deduction, Tax = Gross Salary × taxRate, và Net Salary = Gross Salary - Tax. AI cũng giải thích các thành phần như overtime pay, absent deduction, bonus và tax.</t>
+  </si>
+  <si>
+    <t>Critical Thinking:
+Tôi không copy công thức AI một cách máy móc. Tôi so sánh gợi ý của AI với yêu cầu project và nhận ra AI chỉ đưa công thức tổng quát, còn project cần công thức chi tiết cho từng thành phần lương.
+Contextualization:
+Công thức AI đưa ra giống với công thức cuối về cấu trúc chính: lương cơ bản, overtime, bonus, khấu trừ vắng, thuế và lương thực nhận. Tuy nhiên, công thức cuối của nhóm chi tiết hơn vì xác định rõ cách tính từng phần như baseSalary × ngàyLàmViệc / 26, overtime theo lương giờ × 1.5, khấu trừ vắng theo lương ngày, bonus đi đủ và thuế 10% khi lương trên 11 triệu.
+Decision:
+Tôi dùng công thức AI như khung tham khảo, nhưng triển khai theo công thức chi tiết mà nhóm đã chốt. Logic tính lương sẽ được đặt trong SalaryCalculator thuộc Model/Service layer để đúng yêu cầu MVC.</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>KNOWLEDGE BUILDING / CORE CONCEPT</t>
+  </si>
+  <si>
+    <t>Tôi cần hiểu khái niệm race condition vì đây là vấn đề cốt lõi của đề tài Payroll Simulation. Nếu không hiểu race condition thì sẽ khó giải thích vì sao hệ thống cần các cơ chế đồng bộ như synchronized, optimistic locking và file lock.</t>
+  </si>
+  <si>
+    <t>race condiction là gì</t>
+  </si>
+  <si>
+    <t>AI giải thích race condition là lỗi xảy ra khi nhiều thread cùng truy cập và cập nhật chung một dữ liệu tại cùng thời điểm mà không có cơ chế đồng bộ. Trong đề tài Payroll, race condition có thể gây ra hai lỗi chính: Double Payment khi nhiều thread cùng xử lý một PayrollEntry đang PENDING, và Wrong Leave Deduction khi nhiều thread cùng trừ ngày phép của một nhân viên.</t>
+  </si>
+  <si>
+    <t>Tôi dùng câu trả lời của AI để hiểu rõ bản chất của race condition trong bối cảnh project. Sau đó tôi liên hệ trực tiếp với đề tài của nhóm: payroll_entries.csv có thể bị xử lý trùng gây Double Payment, còn leave_balances.csv có thể bị ghi đè gây Wrong Leave Deduction. Từ đó tôi hiểu vì sao phần Synchronization &amp; Simulation Area là trọng tâm của hệ thống.</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>DESIGN / FLOWCHART GENERATION</t>
+  </si>
+  <si>
+    <t>Payroll Processing Flow</t>
+  </si>
+  <si>
+    <t>Tôi cần tạo flowchart cho luồng xử lý bảng lương hàng tháng vì đây là một trong các flowchart bắt buộc của đồ án. Tôi muốn hiểu thứ tự xử lý payroll từ dữ liệu nhân viên, attendance, tính lương đến lưu kết quả vào CSV.</t>
+  </si>
+  <si>
+    <t>vẽ cho tôi Luồng Xử lý Bảng Lương Hàng Tháng (Monthly Payroll Flow) bằng mã mermaid</t>
+  </si>
+  <si>
+    <t>AI tạo flowchart Mermaid cho Monthly Payroll Flow, gồm các bước: Load Employee Data, Load Attendance Records, Calculate Working Hours, Calculate Overtime Pay, Calculate Absent Deduction, Calculate Bonus, Calculate Gross Salary, Calculate Tax, Calculate Net Salary, Generate PayrollEntry, Save payroll_entries.csv và Generate Payroll Report.</t>
+  </si>
+  <si>
+    <t>Tôi dùng flowchart AI tạo ra để hiểu trình tự xử lý bảng lương hàng tháng. Sau đó tôi kiểm tra lại với yêu cầu project và xác định các bước tính lương chi tiết sẽ thuộc về business logic trong Model/Service, không đặt trong Controller hoặc View. Flowchart này giúp tôi hình dung rõ hơn luồng payroll trước khi thiết kế class SalaryCalculator, PayrollEntry và PayrollController.</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -2119,33 +2184,75 @@
       <c r="H9" s="14"/>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:8">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="A10" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="H10" s="14"/>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:8">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
+      <c r="A11" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="H11" s="14"/>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:8">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="A12" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="H12" s="14"/>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:8">
@@ -2311,32 +2418,32 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
@@ -2344,19 +2451,19 @@
         <v>70</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2533,73 +2640,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="14" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="14" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2626,42 +2733,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -2669,13 +2776,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -2683,13 +2790,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
@@ -2697,13 +2804,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>36</v>
@@ -2711,13 +2818,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>36</v>
@@ -2725,32 +2832,32 @@
     </row>
     <row r="12" ht="18" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
@@ -2758,13 +2865,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>36</v>
@@ -2772,13 +2879,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>36</v>
@@ -2786,13 +2893,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>36</v>
@@ -2800,13 +2907,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>36</v>
@@ -2814,27 +2921,27 @@
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
@@ -2842,13 +2949,13 @@
         <v>48</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/LuongTrieuVy_ai_log.xlsx
+++ b/ai_logs/LuongTrieuVy_ai_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="10440" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -203,76 +203,7 @@
     <t>001</t>
   </si>
   <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>PROBLEM-SOLVING</t>
-  </si>
-  <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
     <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
   </si>
   <si>
     <t>Use Case Review</t>
@@ -314,6 +245,9 @@
 Decision: Tôi chỉnh bản cuối theo hướng user-facing hơn: chỉ thể hiện những chức năng actor có thể dùng, bỏ bớt các bước xử lý nội bộ, giảm mũi tên chồng chéo và làm rõ từng khu vực nghiệp vụ. Quyết định này giúp Use Case Diagram đúng chuẩn UML hơn và phù hợp hơn với mục tiêu báo cáo LAB211.</t>
   </si>
   <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>KNOWLEDGE BUILDING / DESIGN DECISION</t>
   </si>
   <si>
@@ -330,6 +264,9 @@
   </si>
   <si>
     <t>Critical Thinking: Sau khi hiểu rõ 4 cơ chế, tôi nhận ra chúng là các lựa chọn kỹ thuật bên trong Simulator, không phải chức năng độc lập mà người dùng thao tác trực tiếp. Vì Use Case Diagram nên tập trung vào user-facing functions, tôi quyết định không vẽ riêng Apply NO_LOCK, Apply SYNCHRONIZED, Apply OPTIMISTIC_LOCKING, Apply FILE_LOCK như các use case chính trong bản cuối. Contextualization: Trong đồ án LAB211, các cơ chế này vẫn rất quan trọng để thuyết trình và implement ở Repository/Simulator, nhưng trên Use Case Diagram chỉ cần thể hiện chức năng tổng quát như Run Payroll Simulation hoặc Select Sync Mechanism. Creative Synthesis: Tôi dùng kiến thức AI giải thích để hiểu nội dung kỹ thuật, nhưng khi thiết kế sơ đồ, tôi chuyển chúng thành phần mô tả/ghi chú hoặc logic bên trong thay vì oval use case riêng. Decision: Bản cuối loại bớt các cơ chế sync khỏi use case chính để sơ đồ đúng chuẩn UML hơn, tránh nhầm giữa chức năng người dùng và chi tiết implementation.</t>
+  </si>
+  <si>
+    <t>003</t>
   </si>
   <si>
     <t>KNOWLEDGE BUILDING / ARCHITECTURE EXPLORATION</t>
@@ -2034,59 +1971,55 @@
       </c>
     </row>
     <row r="4" ht="100" customHeight="1" spans="1:8">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="23" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="14" t="s">
         <v>62</v>
       </c>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" ht="100" customHeight="1" spans="1:8">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="23" t="s">
         <v>63</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="14" t="s">
         <v>69</v>
       </c>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" ht="100" customHeight="1" spans="1:8">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="23" t="s">
         <v>70</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -2107,152 +2040,108 @@
       <c r="G6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
       <c r="A7" s="23" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" s="14"/>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:8">
       <c r="A8" s="23" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" s="14"/>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:8">
       <c r="A9" s="23" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H9" s="14"/>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:8">
-      <c r="A10" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>101</v>
-      </c>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="14"/>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:8">
-      <c r="A11" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>107</v>
-      </c>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="14"/>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:8">
-      <c r="A12" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>114</v>
-      </c>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="14"/>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:8">
@@ -2365,36 +2254,9 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
     </row>
-    <row r="24" ht="80" customHeight="1" spans="1:8">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" ht="80" customHeight="1" spans="1:8">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" ht="80" customHeight="1" spans="1:8">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-    </row>
+    <row r="24" ht="80" customHeight="1"/>
+    <row r="25" ht="80" customHeight="1"/>
+    <row r="26" ht="80" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
@@ -2418,32 +2280,32 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
@@ -2451,19 +2313,19 @@
         <v>70</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2640,73 +2502,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="14" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="14" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="14" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2733,42 +2595,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -2776,13 +2638,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -2790,13 +2652,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
@@ -2804,13 +2666,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>36</v>
@@ -2818,13 +2680,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>36</v>
@@ -2832,32 +2694,32 @@
     </row>
     <row r="12" ht="18" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
@@ -2865,13 +2727,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>36</v>
@@ -2879,13 +2741,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>36</v>
@@ -2893,13 +2755,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>36</v>
@@ -2907,13 +2769,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>36</v>
@@ -2921,27 +2783,27 @@
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" ht="43.2" spans="1:4">
@@ -2949,13 +2811,13 @@
         <v>48</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/LuongTrieuVy_ai_log.xlsx
+++ b/ai_logs/LuongTrieuVy_ai_log.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\LAB211-Nhom-5\ai_logs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC4B38F-1AA0-42EF-A643-E60CB5C5BE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -27,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -309,6 +305,11 @@
     <t>AI đề xuất công thức tính lương gồm: Gross Salary = Base Salary + Overtime Pay + Bonus - Absent Deduction, Tax = Gross Salary × taxRate, và Net Salary = Gross Salary - Tax. AI cũng giải thích các thành phần như overtime pay, absent deduction, bonus và tax.</t>
   </si>
   <si>
+    <t>Tôi không sao chép công thức tổng quan của AI một cách máy móc. Khi phân tích sâu vào logic code thực tế, tôi phát hiện một lỗi logic nghiêm trọng nếu dùng nguyên công thức đề xuất của AI (Gross = Base + Overtime + Bonus - Absent Deduction): Nếu workDays vốn đã là số ngày đi làm thực tế (tức là đã không tính ngày nghỉ rồi), mà lại trừ thêm một khoản Absent Deduction nữa thì nhân viên sẽ bị khấu trừ trùng lặp tận 2 lần cho cùng một ngày nghỉ.
+Decision:
+Tôi đã chủ động loại bỏ hoàn toàn phần khấu trừ (Absent Deduction) ra khỏi công thức. Thay vào đó, hệ thống sẽ tính lương chuẩn xác bằng cách lấy lương cơ bản chia cho số ngày quy định (26 ngày) rồi nhân trực tiếp với số ngày đi làm thực tế (workDays), vừa tinh gọn code vừa đảm bảo tính công bằng, hợp lý.</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
@@ -346,186 +347,6 @@
   </si>
   <si>
     <t>Tôi dùng flowchart AI tạo ra để hiểu trình tự xử lý bảng lương hàng tháng. Sau đó tôi kiểm tra lại với yêu cầu project và xác định các bước tính lương chi tiết sẽ thuộc về business logic trong Model/Service, không đặt trong Controller hoặc View. Flowchart này giúp tôi hình dung rõ hơn luồng payroll trước khi thiết kế class SalaryCalculator, PayrollEntry và PayrollController.</t>
-  </si>
-  <si>
-    <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
-  </si>
-  <si>
-    <t>MỖI PROJECT PHẢI PHÁT HIỆN ÍT NHẤT: Lab (≥1), Assignment (≥2), Project (≥3) cases hallucination</t>
-  </si>
-  <si>
-    <t>Entry # (from Sheet 2)</t>
-  </si>
-  <si>
-    <t>Hallucination Type</t>
-  </si>
-  <si>
-    <t>AI's Claim</t>
-  </si>
-  <si>
-    <t>Reality Check</t>
-  </si>
-  <si>
-    <t>How Detected</t>
-  </si>
-  <si>
-    <t>Corrective Action</t>
-  </si>
-  <si>
-    <t>Fabrication</t>
-  </si>
-  <si>
-    <t>HALLUCINATION TYPES REFERENCE:</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>AI tạo ra thông tin không tồn tại</t>
-  </si>
-  <si>
-    <t>Fake papers, fake APIs, fake data</t>
-  </si>
-  <si>
-    <t>Oversimplification</t>
-  </si>
-  <si>
-    <t>AI bỏ qua edge cases, exceptions</t>
-  </si>
-  <si>
-    <t>Code không handle array rỗng</t>
-  </si>
-  <si>
-    <t>Logic Error</t>
-  </si>
-  <si>
-    <t>AI đưa kết luận sai về 'best practice'</t>
-  </si>
-  <si>
-    <t>'XGBoost always best' → Sai</t>
-  </si>
-  <si>
-    <t>Outdated Info</t>
-  </si>
-  <si>
-    <t>AI dùng thông tin cũ, không còn đúng</t>
-  </si>
-  <si>
-    <t>Old API syntax, deprecated methods</t>
-  </si>
-  <si>
-    <t>Context Misunderstanding</t>
-  </si>
-  <si>
-    <t>AI không hiểu đúng bối cảnh</t>
-  </si>
-  <si>
-    <t>Không biết business constraints</t>
-  </si>
-  <si>
-    <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
-  </si>
-  <si>
-    <t>Kiểm tra kỹ trước khi nộp. MỖI ENTRY phải pass ≥4/5 tiêu chí dưới đây.</t>
-  </si>
-  <si>
-    <t>A. KIỂM TRA CHẤT LƯỢNG MỖI ENTRY (Pass ≥4/5)</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Tiêu chí</t>
-  </si>
-  <si>
-    <t>Pass?</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
-  </si>
-  <si>
-    <t>☐</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Nếu không có prompt này, project có thay đổi về architecture/design?</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Tôi có thể giải thích lý do chọn/không chọn gợi ý của AI?</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Prompt này phản ánh tư duy phản biện, không chỉ copy AI?</t>
-  </si>
-  <si>
-    <t>B. KIỂM TRA TỔNG THỂ LOG</t>
-  </si>
-  <si>
-    <t>Current Value</t>
-  </si>
-  <si>
-    <t>Số lượng entries nằm trong range (min-max)?</t>
-  </si>
-  <si>
-    <t>Mỗi DTC component có ít nhất 1 core prompt?</t>
-  </si>
-  <si>
-    <t>Đã phát hiện ≥ số lượng hallucination yêu cầu?</t>
-  </si>
-  <si>
-    <t>Mỗi entry đều có Human Delta đầy đủ (4 câu hỏi)?</t>
-  </si>
-  <si>
-    <t>Có evidence cho ≥70% entries?</t>
-  </si>
-  <si>
-    <t>⚠️ LƯU Ý QUAN TRỌNG:</t>
-  </si>
-  <si>
-    <t>Nếu entry KHÔNG pass ≥4/5 tiêu chí → LOẠI BỎ, không ghi vào Log</t>
-  </si>
-  <si>
-    <t>Nếu FAIL ≥2 tiêu chí tổng thể → AI Reflection = 0 điểm (mất 30%)</t>
-  </si>
-  <si>
-    <t>C. CHUẨN BỊ CHO ORAL VIVAS (Q&amp;A)</t>
-  </si>
-  <si>
-    <t>Giảng viên sẽ hỏi ngẫu nhiên về 3-5 entries. Tự hỏi bản thân:</t>
-  </si>
-  <si>
-    <t>Tôi có thể giải thích tại sao chọn approach này?</t>
-  </si>
-  <si>
-    <t>Tôi có nhớ AI response?</t>
-  </si>
-  <si>
-    <t>Tôi có evidence?</t>
   </si>
   <si>
     <t>007</t>
@@ -582,9 +403,28 @@
 AI đã hướng dẫn cách cô đọng lại class và chỉ ra lỗi kiến trúc khi để Controller giữ biến của View.</t>
   </si>
   <si>
-    <t>Tôi không sao chép công thức tổng quan của AI một cách máy móc. Khi phân tích sâu vào logic code thực tế, tôi phát hiện một lỗi logic nghiêm trọng nếu dùng nguyên công thức đề xuất của AI (Gross = Base + Overtime + Bonus - Absent Deduction): Nếu workDays vốn đã là số ngày đi làm thực tế (tức là đã không tính ngày nghỉ rồi), mà lại trừ thêm một khoản Absent Deduction nữa thì nhân viên sẽ bị khấu trừ trùng lặp tận 2 lần cho cùng một ngày nghỉ.
-Decision:
-Tôi đã chủ động loại bỏ hoàn toàn phần khấu trừ (Absent Deduction) ra khỏi công thức. Thay vào đó, hệ thống sẽ tính lương chuẩn xác bằng cách lấy lương cơ bản chia cho số ngày quy định (26 ngày) rồi nhân trực tiếp với số ngày đi làm thực tế (workDays), vừa tinh gọn code vừa đảm bảo tính công bằng, hợp lý.</t>
+    <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
+  </si>
+  <si>
+    <t>MỖI PROJECT PHẢI PHÁT HIỆN ÍT NHẤT: Lab (≥1), Assignment (≥2), Project (≥3) cases hallucination</t>
+  </si>
+  <si>
+    <t>Entry # (from Sheet 2)</t>
+  </si>
+  <si>
+    <t>Hallucination Type</t>
+  </si>
+  <si>
+    <t>AI's Claim</t>
+  </si>
+  <si>
+    <t>Reality Check</t>
+  </si>
+  <si>
+    <t>How Detected</t>
+  </si>
+  <si>
+    <t>Corrective Action</t>
   </si>
   <si>
     <t>Logic &amp; Business Flaw</t>
@@ -603,20 +443,180 @@
   </si>
   <si>
     <t>Loại bỏ hoàn toàn thành phần Absent Deduction ra khỏi công thức tính toán trong class xử lý lương.Sửa lại logic tính lương chuẩn xác và tinh gọn hơn: Tính trực tiếp phần lương cơ bản theo ngày công thực tế:BaseSalaryPaid = BaseSalary * workDays / 26và công thức Gross sẽ không còn phần trừ lặp nữa:Gross = BaseSalaryPaid + Overtime + Bonus</t>
+  </si>
+  <si>
+    <t>HALLUCINATION TYPES REFERENCE:</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Fabrication</t>
+  </si>
+  <si>
+    <t>AI tạo ra thông tin không tồn tại</t>
+  </si>
+  <si>
+    <t>Fake papers, fake APIs, fake data</t>
+  </si>
+  <si>
+    <t>Oversimplification</t>
+  </si>
+  <si>
+    <t>AI bỏ qua edge cases, exceptions</t>
+  </si>
+  <si>
+    <t>Code không handle array rỗng</t>
+  </si>
+  <si>
+    <t>Logic Error</t>
+  </si>
+  <si>
+    <t>AI đưa kết luận sai về 'best practice'</t>
+  </si>
+  <si>
+    <t>'XGBoost always best' → Sai</t>
+  </si>
+  <si>
+    <t>Outdated Info</t>
+  </si>
+  <si>
+    <t>AI dùng thông tin cũ, không còn đúng</t>
+  </si>
+  <si>
+    <t>Old API syntax, deprecated methods</t>
+  </si>
+  <si>
+    <t>Context Misunderstanding</t>
+  </si>
+  <si>
+    <t>AI không hiểu đúng bối cảnh</t>
+  </si>
+  <si>
+    <t>Không biết business constraints</t>
+  </si>
+  <si>
+    <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
+  </si>
+  <si>
+    <t>Kiểm tra kỹ trước khi nộp. MỖI ENTRY phải pass ≥4/5 tiêu chí dưới đây.</t>
+  </si>
+  <si>
+    <t>A. KIỂM TRA CHẤT LƯỢNG MỖI ENTRY (Pass ≥4/5)</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Pass?</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
+  </si>
+  <si>
+    <t>☐</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Nếu không có prompt này, project có thay đổi về architecture/design?</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Tôi có thể giải thích lý do chọn/không chọn gợi ý của AI?</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Prompt này phản ánh tư duy phản biện, không chỉ copy AI?</t>
+  </si>
+  <si>
+    <t>B. KIỂM TRA TỔNG THỂ LOG</t>
+  </si>
+  <si>
+    <t>Current Value</t>
+  </si>
+  <si>
+    <t>Số lượng entries nằm trong range (min-max)?</t>
+  </si>
+  <si>
+    <t>Mỗi DTC component có ít nhất 1 core prompt?</t>
+  </si>
+  <si>
+    <t>Đã phát hiện ≥ số lượng hallucination yêu cầu?</t>
+  </si>
+  <si>
+    <t>Mỗi entry đều có Human Delta đầy đủ (4 câu hỏi)?</t>
+  </si>
+  <si>
+    <t>Có evidence cho ≥70% entries?</t>
+  </si>
+  <si>
+    <t>⚠️ LƯU Ý QUAN TRỌNG:</t>
+  </si>
+  <si>
+    <t>Nếu entry KHÔNG pass ≥4/5 tiêu chí → LOẠI BỎ, không ghi vào Log</t>
+  </si>
+  <si>
+    <t>Nếu FAIL ≥2 tiêu chí tổng thể → AI Reflection = 0 điểm (mất 30%)</t>
+  </si>
+  <si>
+    <t>C. CHUẨN BỊ CHO ORAL VIVAS (Q&amp;A)</t>
+  </si>
+  <si>
+    <t>Giảng viên sẽ hỏi ngẫu nhiên về 3-5 entries. Tự hỏi bản thân:</t>
+  </si>
+  <si>
+    <t>Tôi có thể giải thích tại sao chọn approach này?</t>
+  </si>
+  <si>
+    <t>Tôi có nhớ AI response?</t>
+  </si>
+  <si>
+    <t>Tôi có evidence?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -624,7 +624,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF2E75B6"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -632,7 +632,7 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -640,7 +640,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -648,13 +648,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -662,28 +662,28 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -691,7 +691,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -700,7 +700,7 @@
       <i/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -708,12 +708,156 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,8 +882,194 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -762,12 +1092,260 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -796,51 +1374,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -856,19 +1471,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Hình ảnh 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F7EBC4C-DDFD-FF10-CF34-053D6F3B6193}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Hình ảnh 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -881,8 +1490,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14023731" y="7888654"/>
-          <a:ext cx="1528884" cy="1018930"/>
+          <a:off x="12618720" y="8014335"/>
+          <a:ext cx="1376045" cy="1022985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -901,24 +1510,18 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>681</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1016046</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Hình ảnh 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13C617B4-8664-8BFB-306E-1993993A7E42}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Hình ảnh 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -931,8 +1534,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14023732" y="8899769"/>
-          <a:ext cx="1523999" cy="1011797"/>
+          <a:off x="12618720" y="9029700"/>
+          <a:ext cx="1371600" cy="1016000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -956,19 +1559,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Hình ảnh 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3F63D00-CE40-6966-E597-5E83C9E3D087}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="7" name="Hình ảnh 6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -981,12 +1578,210 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14023731" y="4855308"/>
-          <a:ext cx="1528883" cy="1014486"/>
+          <a:off x="12618720" y="4968240"/>
+          <a:ext cx="1376045" cy="1018540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>8255</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1261110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-07-21 230938"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12630785" y="1166495"/>
+          <a:ext cx="1367790" cy="1250950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6985</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1229360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>18415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Screenshot 2026-07-21 231331"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12625705" y="2385695"/>
+          <a:ext cx="1367790" cy="1330325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1267460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>49530</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1263650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5" descr="Screenshot 2026-07-21 231814"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12631420" y="3694430"/>
+          <a:ext cx="1408430" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>10795</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1011555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12630785" y="5991225"/>
+          <a:ext cx="1370330" cy="1003935"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>13335</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>954405</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1365885</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>119380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12632055" y="6938010"/>
+          <a:ext cx="1352550" cy="1195705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1273,14 +2068,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1289,226 +2084,221 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="21" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.399999999999999">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="3" ht="18" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="18" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.399999999999999">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="18" spans="1:5">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="15" t="e">
+      <c r="C12" s="20" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.399999999999999">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="18" spans="1:5">
+      <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.399999999999999">
-      <c r="A22" s="1" t="s">
+    <row r="22" ht="18" spans="1:4">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="22">
         <v>0</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="22">
         <v>0</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="22">
         <v>0</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="22">
         <v>0</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1517,13 +2307,15 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1534,690 +2326,668 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="21" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="21" t="s">
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" ht="40.05" customHeight="1" spans="1:8">
+      <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="100.05" customHeight="1">
-      <c r="A4" s="18" t="s">
+    <row r="4" ht="100.05" customHeight="1" spans="1:8">
+      <c r="A4" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" ht="100.05" customHeight="1" spans="1:8">
+      <c r="A5" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="12"/>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" ht="100.05" customHeight="1" spans="1:8">
+      <c r="A6" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A7" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="G7" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A8" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A9" s="18" t="s">
+      <c r="G8" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A9" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A10" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A11" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1"/>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1"/>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1"/>
+      <c r="G9" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A10" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" ht="79.95" customHeight="1" spans="1:8">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" ht="79.95" customHeight="1"/>
+    <row r="25" ht="79.95" customHeight="1"/>
+    <row r="26" ht="79.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+    <row r="1" ht="21" spans="1:6">
+      <c r="A1" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="223.2" customHeight="1">
-      <c r="A4" s="18" t="s">
+      <c r="A2" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" ht="40.05" customHeight="1" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" ht="223.2" customHeight="1" spans="1:6">
+      <c r="A4" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="115.8" customHeight="1">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
+      <c r="B4" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" ht="115.8" customHeight="1" spans="1:6">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.399999999999999">
-      <c r="A30" s="1" t="s">
-        <v>105</v>
+    <row r="6" ht="60" customHeight="1" spans="1:6">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:6">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:6">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:6">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:6">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:6">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:6">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:6">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:6">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:6">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:6">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:6">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:6">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:6">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:6">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:6">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:6">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:6">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:6">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="30" ht="18" spans="1:6">
+      <c r="A30" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27.6">
-      <c r="A32" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="27.6">
-      <c r="A33" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="27.6">
-      <c r="A34" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="27.6">
-      <c r="A35" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="41.4">
-      <c r="A36" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>122</v>
+      <c r="A31" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:6">
+      <c r="A32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" ht="28.8" spans="1:3">
+      <c r="A33" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" ht="28.8" spans="1:3">
+      <c r="A34" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" ht="28.8" spans="1:3">
+      <c r="A35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" ht="43.2" spans="1:3">
+      <c r="A36" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2226,13 +2996,15 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2240,278 +3012,272 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+    <row r="1" ht="21" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-    </row>
-    <row r="4" spans="1:4" ht="17.399999999999999">
-      <c r="A4" s="1" t="s">
-        <v>125</v>
+      <c r="A2" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>129</v>
+      <c r="A5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="A6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="A7" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="A8" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="A9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="A10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="17.399999999999999">
-      <c r="A12" s="1" t="s">
-        <v>141</v>
+    <row r="12" ht="18" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>142</v>
+      <c r="A13" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="A14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="A15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="A16" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="A17" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="A18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.6">
-      <c r="A20" s="6" t="s">
-        <v>148</v>
+    <row r="20" ht="15.6" spans="1:4">
+      <c r="A20" s="8" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="7" t="s">
-        <v>149</v>
+      <c r="A21" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17.399999999999999">
-      <c r="A25" s="1" t="s">
-        <v>151</v>
+      <c r="A22" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="55.2">
-      <c r="A27" s="9" t="s">
+      <c r="A26" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" ht="43.2" spans="1:4">
+      <c r="A27" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>155</v>
+      <c r="B27" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2521,5 +3287,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ai_logs/LuongTrieuVy_ai_log.xlsx
+++ b/ai_logs/LuongTrieuVy_ai_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="10500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="181">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -599,6 +599,21 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
+  </si>
+  <si>
+    <t>Tôi dùng AI để review Use Case Diagram nhằm phát hiện actor, include/extend và luồng xử lý chưa đúng. Sau đó tôi đối chiếu với UML và chỉnh lại theo yêu cầu đề tài thay vì làm theo toàn bộ góp ý của AI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">có </t>
+  </si>
+  <si>
+    <t>có</t>
+  </si>
+  <si>
+    <t>Tôi dùng AI để gợi ý Flowchart xử lý bảng lương, sau đó chỉnh lại theo đúng luồng xử lý của source code và Repository thay vì dùng nguyên flow AI sinh ra.</t>
+  </si>
+  <si>
+    <t>Tôi hỏi AI để hiểu 4 cơ chế đồng bộ (NO_LOCK, SYNCHRONIZED, OPTIMISTIC, FILE_LOCK), sau đó chỉ chọn các cơ chế phù hợp với chức năng Simulation của project thay vì áp dụng cho toàn bộ hệ thống.</t>
   </si>
 </sst>
 </file>
@@ -1392,6 +1407,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3239,46 +3257,46 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="13" t="s">
-        <v>56</v>
+    <row r="28" ht="43.2" spans="1:4">
+      <c r="A28" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" ht="43.2" spans="1:4">
+      <c r="A29" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" ht="43.2" spans="1:4">
+      <c r="A30" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="B30" s="14" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
